--- a/data/samples/sample.xlsx
+++ b/data/samples/sample.xlsx
@@ -123,6 +123,181 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Daily Latency (ms)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Notes'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Notes'!$A$2:$A$86</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Notes'!$C$2:$C$86</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Day</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>LatencyMs</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4762500" cy="2857500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -475,6 +650,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -484,49 +660,1133 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:C86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Prepared by Finance</t>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>LatencyMs</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Quarter</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Headcount</t>
-        </is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>181</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
         <v>42</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
         <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>999</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>